--- a/fotos_lotes_import/Import_imoveis.xlsx
+++ b/fotos_lotes_import/Import_imoveis.xlsx
@@ -13,10 +13,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={7a26049a-7e5b-4fc1-b16d-b2991a7b81e1}</author>
+    <author>tc={8b788eee-488e-49ac-9e87-f270e83bd0dc}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{7a26049a-7e5b-4fc1-b16d-b2991a7b81e1}" ref="A1">
+    <comment authorId="0" xr:uid="{8b788eee-488e-49ac-9e87-f270e83bd0dc}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -84,7 +84,7 @@
     <t>ativa</t>
   </si>
   <si>
-    <t>propietario</t>
+    <t>proprietario_id</t>
   </si>
   <si>
     <t>IMO101</t>
@@ -246,7 +246,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Missão &amp; Estradas" id="{5cfc722a-fb77-4c32-bf19-1d526e52f6cc}" providerId="google-sheets"/>
+  <x18tc:person displayName="Missão &amp; Estradas" id="{66927ca6-4a96-4ad3-957b-1445b0367814}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -446,7 +446,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A1" dT="2026-09-24T19:14:55.00" personId="{5cfc722a-fb77-4c32-bf19-1d526e52f6cc}" id="{7a26049a-7e5b-4fc1-b16d-b2991a7b81e1}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-09-24T19:14:55.00" personId="{66927ca6-4a96-4ad3-957b-1445b0367814}" id="{8b788eee-488e-49ac-9e87-f270e83bd0dc}" done="0">
     <x18tc:text xml:space="preserve">codigo_ref (Ex: IMO101)
 imobiliaria_id (Ex: 6bbb3039-ef41-4377-b435-f1ed386c2e36)
 titulo (Ex: Casa de Praia com Vista)
